--- a/src/AssetDesk.Web/wwwroot/templates/Asset_Upload_Template.xlsx
+++ b/src/AssetDesk.Web/wwwroot/templates/Asset_Upload_Template.xlsx
@@ -19,25 +19,25 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t xml:space="preserve">  • Currency: PHP, USD</x:t>
+    <x:t xml:space="preserve">  • Currency defaults to PHP if left blank.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">  • ExchangeRate is pesos per 1 unit of Currency — required for any currency other than PHP.</x:t>
   </x:si>
   <x:si>
-    <x:t>USD</x:t>
+    <x:t xml:space="preserve">  • Totals are reported in pesos; each asset keeps the price and currency you enter here.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">  • Currency: PHP, USD</x:t>
   </x:si>
   <x:si>
     <x:t>ExchangeRate</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">  • Currency defaults to PHP if left blank.</x:t>
+    <x:t>PHP</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">  • Totals are reported in pesos; each asset keeps the price and currency you enter here.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHP</x:t>
+    <x:t>USD</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -667,7 +667,7 @@
     <x:pageSetUpPr/>
   </x:sheetPr>
   <x:dimension ref="A1:A25"/>
-  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="110" style="0" customWidth="1"/>
   </x:cols>
@@ -788,7 +788,7 @@
     </x:row>
     <x:row r="19" spans="1:1">
       <x:c r="A19" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:1">
@@ -798,7 +798,7 @@
     </x:row>
     <x:row r="21" spans="1:1">
       <x:c r="A21" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:1">
@@ -834,7 +834,7 @@
     </x:row>
     <x:row r="27" spans="1:1">
       <x:c r="A27" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -853,7 +853,7 @@
     <x:pageSetUpPr/>
   </x:sheetPr>
   <x:dimension ref="A1:O2"/>
-  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="22" style="0" customWidth="1"/>
     <x:col min="2" max="3" width="14" style="0" customWidth="1"/>
@@ -917,7 +917,7 @@
         </x:is>
       </x:c>
       <x:c r="J1" s="11" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K1" s="11" t="inlineStr">
         <x:is>
@@ -1027,7 +1027,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="3">
+  <x:dataValidations count="4">
     <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Value must come from the Reference sheet." promptTitle="Pick from list" prompt="Choose a device type" sqref="B2:B1000">
       <x:formula1>=Reference!$A$2:$A$12</x:formula1>
       <x:formula2/>
@@ -1036,8 +1036,12 @@
       <x:formula1>=Reference!$B$2:$B$6</x:formula1>
       <x:formula2/>
     </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Value must come from the Reference sheet." promptTitle="Pick from list" prompt="Choose a currency" sqref="I2:J1000">
+    <x:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Value must come from the Reference sheet." promptTitle="Pick from list" prompt="Choose a currency" sqref="I2:I1000">
       <x:formula1>=Reference!$C$2:$C$3</x:formula1>
+      <x:formula2/>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" errorStyle="stop" operator="greaterThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Value must be a number greater than 0." promptTitle="Enter a number" prompt="Enter the exchange rate to PHP" sqref="J2:J1000">
+      <x:formula1>0</x:formula1>
       <x:formula2/>
     </x:dataValidation>
   </x:dataValidations>
@@ -1057,7 +1061,7 @@
     <x:pageSetUpPr/>
   </x:sheetPr>
   <x:dimension ref="A1:C12"/>
-  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="2" width="16" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="12" style="0" customWidth="1"/>
@@ -1092,7 +1096,7 @@
         </x:is>
       </x:c>
       <x:c r="C2" s="10" t="s">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -1107,7 +1111,7 @@
         </x:is>
       </x:c>
       <x:c r="C3" s="10" t="s">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
